--- a/Outputs/Recycling_Plot_Data/ACCII/07_Exported_Minerals_data_ACCII.xlsx
+++ b/Outputs/Recycling_Plot_Data/ACCII/07_Exported_Minerals_data_ACCII.xlsx
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="E14">
-        <v>0.9009980576871597</v>
+        <v>0.8179068015640414</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="E15">
-        <v>5.193578180553076</v>
+        <v>4.737047230507918</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="E16">
-        <v>10.43920331196639</v>
+        <v>9.514600774056417</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="E17">
-        <v>0.9792469400876449</v>
+        <v>0.8920887535360503</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="E18">
-        <v>0.4073871473691246</v>
+        <v>0.3700296871403082</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="E19">
-        <v>4.586848620305114</v>
+        <v>4.164107537328197</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="E20">
-        <v>0.8996026045165876</v>
+        <v>0.8186825891858751</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="E21">
-        <v>5.375697597054709</v>
+        <v>4.918141178820909</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="E22">
-        <v>10.74330182588638</v>
+        <v>9.821064971355852</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         </is>
       </c>
       <c r="E23">
-        <v>1.004174727277667</v>
+        <v>0.917494609875468</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         </is>
       </c>
       <c r="E24">
-        <v>0.4037097650764774</v>
+        <v>0.3675698542225368</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="E25">
-        <v>4.576746687727856</v>
+        <v>4.165301171276465</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="E26">
-        <v>0.7098357962584795</v>
+        <v>0.5841231834957982</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         </is>
       </c>
       <c r="E27">
-        <v>3.756427174335053</v>
+        <v>3.104266481006996</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         </is>
       </c>
       <c r="E28">
-        <v>7.664335501882549</v>
+        <v>6.329363617580178</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="E29">
-        <v>0.7254340160327736</v>
+        <v>0.5988118952731234</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="E30">
-        <v>0.3221622392208443</v>
+        <v>0.2653148228236872</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="E31">
-        <v>3.633250625765958</v>
+        <v>2.990223589504759</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="E32">
-        <v>0.7238524317048044</v>
+        <v>0.6016212167822776</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="E33">
-        <v>3.966469004763081</v>
+        <v>3.312674138736639</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="E34">
-        <v>8.044692002122639</v>
+        <v>6.713522520813817</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         </is>
       </c>
       <c r="E35">
-        <v>0.7586744604106258</v>
+        <v>0.6328197694765874</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         </is>
       </c>
       <c r="E36">
-        <v>0.3262532695766629</v>
+        <v>0.2713475211724604</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         </is>
       </c>
       <c r="E37">
-        <v>3.703406805012158</v>
+        <v>3.078476845600585</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="E38">
-        <v>3.318473311235622</v>
+        <v>3.187265453235502</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="E39">
-        <v>19.03682797807194</v>
+        <v>18.37653840086151</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="E40">
-        <v>38.39031513868836</v>
+        <v>37.03106187436493</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         </is>
       </c>
       <c r="E41">
-        <v>3.603297992166887</v>
+        <v>3.473961417335015</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="E42">
-        <v>1.550579910396368</v>
+        <v>1.490989918779317</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         </is>
       </c>
       <c r="E43">
-        <v>17.12648055465959</v>
+        <v>16.45429700699306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="E44">
-        <v>3.233920146123212</v>
+        <v>3.105552923866977</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="E45">
-        <v>19.36890980288312</v>
+        <v>18.70712590073203</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="E46">
-        <v>38.79038272949159</v>
+        <v>37.43403695755566</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         </is>
       </c>
       <c r="E47">
-        <v>3.625324272694665</v>
+        <v>3.496598538856822</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="E48">
-        <v>1.499400347165879</v>
+        <v>1.441427059847243</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         </is>
       </c>
       <c r="E49">
-        <v>16.68204236022286</v>
+        <v>16.02481101405744</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         </is>
       </c>
       <c r="E50">
-        <v>3.299890609214671</v>
+        <v>3.113199910116697</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="E51">
-        <v>17.38200300238521</v>
+        <v>16.47267178243888</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="E52">
-        <v>35.57477479797326</v>
+        <v>33.69015352412054</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="E53">
-        <v>3.369029929082495</v>
+        <v>3.189044184063082</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="E54">
-        <v>1.533435042295605</v>
+        <v>1.448529977090618</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         </is>
       </c>
       <c r="E55">
-        <v>17.09189816770557</v>
+        <v>16.13105154199181</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c r="E56">
-        <v>3.23139729184135</v>
+        <v>3.0492865650905</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         </is>
       </c>
       <c r="E57">
-        <v>17.75069874495095</v>
+        <v>16.83898967578286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         </is>
       </c>
       <c r="E58">
-        <v>36.06769631187981</v>
+        <v>34.187785422052</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="E59">
-        <v>3.400833084185816</v>
+        <v>3.221833962766992</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="E60">
-        <v>1.490334906494511</v>
+        <v>1.408015240346161</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
         </is>
       </c>
       <c r="E61">
-        <v>16.73285091905555</v>
+        <v>15.79604404864026</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="E62">
-        <v>6.248334813324202</v>
+        <v>6.054160343657548</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="E63">
-        <v>35.72081039527889</v>
+        <v>34.79614047134235</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         </is>
       </c>
       <c r="E64">
-        <v>72.22678085167705</v>
+        <v>70.30320570932174</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         </is>
       </c>
       <c r="E65">
-        <v>6.781945774224213</v>
+        <v>6.597794744933958</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="E66">
-        <v>2.991154915677516</v>
+        <v>2.902910496024227</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="E67">
-        <v>32.6170007195966</v>
+        <v>31.61983169674962</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         </is>
       </c>
       <c r="E68">
-        <v>6.026819691948941</v>
+        <v>5.836470986116304</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         </is>
       </c>
       <c r="E69">
-        <v>36.28626429861757</v>
+        <v>35.35921243857526</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         </is>
       </c>
       <c r="E70">
-        <v>72.75948796776312</v>
+        <v>70.83930541886295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="E71">
-        <v>6.797063874880971</v>
+        <v>6.613693493879705</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="E72">
-        <v>2.861246227744315</v>
+        <v>2.775210037496258</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         </is>
       </c>
       <c r="E73">
-        <v>31.4513000714817</v>
+        <v>30.47452092998297</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="E74">
-        <v>7.361404826469376</v>
+        <v>6.805195575504961</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         </is>
       </c>
       <c r="E75">
-        <v>38.26017986151567</v>
+        <v>35.69681388667319</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         </is>
       </c>
       <c r="E76">
-        <v>78.52813674772935</v>
+        <v>73.16338755924615</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         </is>
       </c>
       <c r="E77">
-        <v>7.446833066981373</v>
+        <v>6.931335267329806</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         </is>
       </c>
       <c r="E78">
-        <v>3.483058826613486</v>
+        <v>3.231305953676118</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         </is>
       </c>
       <c r="E79">
-        <v>38.20935175720313</v>
+        <v>35.35465004357457</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         </is>
       </c>
       <c r="E80">
-        <v>7.138615458028075</v>
+        <v>6.593119058992168</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         </is>
       </c>
       <c r="E81">
-        <v>38.87657621782797</v>
+        <v>36.30811817257619</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         </is>
       </c>
       <c r="E82">
-        <v>79.1452768742986</v>
+        <v>73.79246840644475</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         </is>
       </c>
       <c r="E83">
-        <v>7.468771736928188</v>
+        <v>6.955659151885282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         </is>
       </c>
       <c r="E84">
-        <v>3.351556562507433</v>
+        <v>3.10590419003401</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         </is>
       </c>
       <c r="E85">
-        <v>37.03897873307472</v>
+        <v>34.24081434726666</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         </is>
       </c>
       <c r="E86">
-        <v>10.85259029918172</v>
+        <v>10.27399651168824</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         </is>
       </c>
       <c r="E87">
-        <v>60.92927684460088</v>
+        <v>58.30526849224177</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="E88">
-        <v>123.6128266895091</v>
+        <v>118.1073848464543</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         </is>
       </c>
       <c r="E89">
-        <v>11.62752554390464</v>
+        <v>11.09755998818112</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         </is>
       </c>
       <c r="E90">
-        <v>5.284688236337585</v>
+        <v>5.023750327372923</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         </is>
       </c>
       <c r="E91">
-        <v>56.74195148295341</v>
+        <v>53.78034784820666</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="E92">
-        <v>10.39953391113218</v>
+        <v>9.829640925196591</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="E93">
-        <v>61.85409924348785</v>
+        <v>59.22540122832569</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="E94">
-        <v>124.3061451830049</v>
+        <v>118.8097316169185</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         </is>
       </c>
       <c r="E95">
-        <v>11.6256560141146</v>
+        <v>11.09757504277932</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         </is>
       </c>
       <c r="E96">
-        <v>5.021033826557808</v>
+        <v>4.765154820426017</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="E97">
-        <v>54.3465258682008</v>
+        <v>51.43148808676072</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="E98">
-        <v>10.91925832919555</v>
+        <v>10.25983115557211</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="E99">
-        <v>57.42556601763847</v>
+        <v>54.45049813674238</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="E100">
-        <v>117.6190498435426</v>
+        <v>111.3705054912351</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="E101">
-        <v>11.13865333567321</v>
+        <v>10.53679918043462</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         </is>
       </c>
       <c r="E102">
-        <v>5.342523277444778</v>
+        <v>5.042830046469668</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         </is>
       </c>
       <c r="E103">
-        <v>56.59656045813976</v>
+        <v>53.2214861870295</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         </is>
       </c>
       <c r="E104">
-        <v>10.46201789685156</v>
+        <v>9.815325547096556</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         </is>
       </c>
       <c r="E105">
-        <v>58.44671445483919</v>
+        <v>55.46533409459666</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="E106">
-        <v>118.4743847486679</v>
+        <v>112.2396270888735</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         </is>
       </c>
       <c r="E107">
-        <v>11.14970027340337</v>
+        <v>10.5506477795457</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         </is>
       </c>
       <c r="E108">
-        <v>5.077646704648617</v>
+        <v>4.785269439866562</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         </is>
       </c>
       <c r="E109">
-        <v>54.19659331458941</v>
+        <v>50.88878277648116</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c r="E110">
-        <v>15.20661681892177</v>
+        <v>14.51946557717974</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="E111">
-        <v>86.01801131782278</v>
+        <v>82.96822163613543</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="E112">
-        <v>174.3041571972972</v>
+        <v>167.8814138893662</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         </is>
       </c>
       <c r="E113">
-        <v>16.38155474279823</v>
+        <v>15.76176206435346</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="E114">
-        <v>7.651226234050535</v>
+        <v>7.341130089311651</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="E115">
-        <v>79.42677533467615</v>
+        <v>75.91734034139586</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="E116">
-        <v>14.38628587737512</v>
+        <v>13.70927927187731</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         </is>
       </c>
       <c r="E117">
-        <v>87.52761033766446</v>
+        <v>84.47195211120651</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         </is>
       </c>
       <c r="E118">
-        <v>175.279976895921</v>
+        <v>168.8671484028346</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         </is>
       </c>
       <c r="E119">
-        <v>16.35505658502912</v>
+        <v>15.73741115073694</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="E120">
-        <v>7.176988967571612</v>
+        <v>6.87284529920939</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         </is>
       </c>
       <c r="E121">
-        <v>75.08719682661366</v>
+        <v>71.63220540299295</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         </is>
       </c>
       <c r="E122">
-        <v>14.64849318168189</v>
+        <v>13.94986552207304</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="E123">
-        <v>77.88337713253303</v>
+        <v>74.78021132925441</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
         </is>
       </c>
       <c r="E124">
-        <v>159.2380079023754</v>
+        <v>152.7025977396175</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="E125">
-        <v>15.06086137246557</v>
+        <v>14.43026605401757</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="E126">
-        <v>7.415926681469545</v>
+        <v>7.097601254193195</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         </is>
       </c>
       <c r="E127">
-        <v>75.86739973240849</v>
+        <v>72.29737248819956</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         </is>
       </c>
       <c r="E128">
-        <v>13.80206909546705</v>
+        <v>13.11793514233659</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         </is>
       </c>
       <c r="E129">
-        <v>79.55888346628305</v>
+        <v>76.44812608471291</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         </is>
       </c>
       <c r="E130">
-        <v>160.4612054104003</v>
+        <v>153.9408162191307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         </is>
       </c>
       <c r="E131">
-        <v>15.05157566330519</v>
+        <v>14.42411334308187</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="E132">
-        <v>6.930297327948232</v>
+        <v>6.620367953015852</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         </is>
       </c>
       <c r="E133">
-        <v>71.43152265570208</v>
+        <v>67.93807106391273</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         </is>
       </c>
       <c r="E134">
-        <v>20.11673402017736</v>
+        <v>19.38716663586849</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         </is>
       </c>
       <c r="E135">
-        <v>114.3525380501587</v>
+        <v>111.1651693619552</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         </is>
       </c>
       <c r="E136">
-        <v>231.5797339341991</v>
+        <v>224.8479989225548</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         </is>
       </c>
       <c r="E137">
-        <v>21.75126959928741</v>
+        <v>21.10047709861482</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="E138">
-        <v>10.45722949838092</v>
+        <v>10.12786500355723</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         </is>
       </c>
       <c r="E139">
-        <v>105.051535202893</v>
+        <v>101.3299005318846</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -4270,7 +4270,7 @@
         </is>
       </c>
       <c r="E140">
-        <v>18.69483189840366</v>
+        <v>17.97661172436119</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         </is>
       </c>
       <c r="E141">
-        <v>116.8025448399304</v>
+        <v>113.6079874398831</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         </is>
       </c>
       <c r="E142">
-        <v>232.9919474977239</v>
+        <v>226.2703068719433</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         </is>
       </c>
       <c r="E143">
-        <v>21.68229084261617</v>
+        <v>21.03381824423318</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         </is>
       </c>
       <c r="E144">
-        <v>9.638892635391034</v>
+        <v>9.316238448776232</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="E145">
-        <v>97.53534991035995</v>
+        <v>93.87474981540034</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         </is>
       </c>
       <c r="E146">
-        <v>18.45369105266041</v>
+        <v>17.79954484148391</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="E147">
-        <v>99.09975627594361</v>
+        <v>96.22649430054835</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         </is>
       </c>
       <c r="E148">
-        <v>202.3869151913724</v>
+        <v>196.322603502628</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         </is>
       </c>
       <c r="E149">
-        <v>19.11969409144779</v>
+        <v>18.53380997414432</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         </is>
       </c>
       <c r="E150">
-        <v>9.659006841929958</v>
+        <v>9.360310877246071</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="E151">
-        <v>95.74306128148748</v>
+        <v>92.40134965352811</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         </is>
       </c>
       <c r="E152">
-        <v>17.02458922346613</v>
+        <v>16.38546550859141</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -4634,7 +4634,7 @@
         </is>
       </c>
       <c r="E153">
-        <v>101.7342037768081</v>
+        <v>98.85243286642374</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         </is>
       </c>
       <c r="E154">
-        <v>204.1188226648912</v>
+        <v>198.0691304068341</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         </is>
       </c>
       <c r="E155">
-        <v>19.07641390301676</v>
+        <v>18.49369970885889</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="E156">
-        <v>8.841705315544225</v>
+        <v>8.551798303798813</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         </is>
       </c>
       <c r="E157">
-        <v>88.24162226731956</v>
+        <v>84.97959138756588</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         </is>
       </c>
       <c r="E158">
-        <v>25.58249437515275</v>
+        <v>24.897407529813</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         </is>
       </c>
       <c r="E159">
-        <v>145.7747137184992</v>
+        <v>142.8150411094536</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         </is>
       </c>
       <c r="E160">
-        <v>295.2880601333818</v>
+        <v>289.0233275544242</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
         </is>
       </c>
       <c r="E161">
-        <v>27.72558434323759</v>
+        <v>27.11915280088469</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         </is>
       </c>
       <c r="E162">
-        <v>13.71542346360354</v>
+        <v>13.40583613572016</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         </is>
       </c>
       <c r="E163">
-        <v>133.9110627333497</v>
+        <v>130.4167332623751</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         </is>
       </c>
       <c r="E164">
-        <v>23.25667234528103</v>
+        <v>22.58338133905063</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="E165">
-        <v>149.6221598260824</v>
+        <v>146.6540615411135</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         </is>
       </c>
       <c r="E166">
-        <v>297.3200994012579</v>
+        <v>291.0643908004842</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         </is>
       </c>
       <c r="E167">
-        <v>27.58970070797674</v>
+        <v>26.98556077323129</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         </is>
       </c>
       <c r="E168">
-        <v>12.37832464393501</v>
+        <v>12.07576979342515</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         </is>
       </c>
       <c r="E169">
-        <v>121.5979081387071</v>
+        <v>118.1673730607109</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         </is>
       </c>
       <c r="E170">
-        <v>22.32816250442728</v>
+        <v>21.78693539394298</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         </is>
       </c>
       <c r="E171">
-        <v>121.1958379794658</v>
+        <v>118.8382586584495</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         </is>
       </c>
       <c r="E172">
-        <v>247.447720651542</v>
+        <v>242.4622488060507</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         </is>
       </c>
       <c r="E173">
-        <v>23.34794664736065</v>
+        <v>22.86583749799237</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         </is>
       </c>
       <c r="E174">
-        <v>12.13094092573432</v>
+        <v>11.88298415874266</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         </is>
       </c>
       <c r="E175">
-        <v>116.6445268583539</v>
+        <v>113.876652265957</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         </is>
       </c>
       <c r="E176">
-        <v>20.10518726992134</v>
+        <v>19.57773730344599</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         </is>
       </c>
       <c r="E177">
-        <v>125.1231617288471</v>
+        <v>122.7568713911581</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         </is>
       </c>
       <c r="E178">
-        <v>249.8185085990223</v>
+        <v>244.8452381341484</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="E179">
-        <v>23.2535739300289</v>
+        <v>22.77427538010268</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="E180">
-        <v>10.84680252468993</v>
+        <v>10.60706721789476</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         </is>
       </c>
       <c r="E181">
-        <v>104.8932891782464</v>
+        <v>102.199268257093</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="E182">
-        <v>31.61309588138804</v>
+        <v>31.04374150118383</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         </is>
       </c>
       <c r="E183">
-        <v>180.5324318560432</v>
+        <v>178.0923105471914</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         </is>
       </c>
       <c r="E184">
-        <v>366.139239028375</v>
+        <v>360.9646325066662</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         </is>
       </c>
       <c r="E185">
-        <v>34.36725583507229</v>
+        <v>33.86588914233681</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         </is>
       </c>
       <c r="E186">
-        <v>17.53801794988927</v>
+        <v>17.2799751141582</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         </is>
       </c>
       <c r="E187">
-        <v>166.7029875818333</v>
+        <v>163.795942526974</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         </is>
       </c>
       <c r="E188">
-        <v>28.0386230384239</v>
+        <v>27.4804801266833</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         </is>
       </c>
       <c r="E189">
-        <v>186.3112961591482</v>
+        <v>183.8618794365802</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         </is>
       </c>
       <c r="E190">
-        <v>368.9838384120065</v>
+        <v>363.8159127470688</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="E191">
-        <v>34.13491212721335</v>
+        <v>33.63556975327199</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         </is>
       </c>
       <c r="E192">
-        <v>15.46223921286476</v>
+        <v>15.21098299737526</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="E193">
-        <v>147.6569310453553</v>
+        <v>144.8112034932958</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         </is>
       </c>
       <c r="E194">
-        <v>26.35406169525601</v>
+        <v>25.95000192557317</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
         </is>
       </c>
       <c r="E195">
-        <v>144.3892077377758</v>
+        <v>142.6397198228352</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         </is>
       </c>
       <c r="E196">
-        <v>295.0131392437929</v>
+        <v>291.3071758755304</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="E197">
-        <v>27.80675521446199</v>
+        <v>27.44813469298753</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         </is>
       </c>
       <c r="E198">
-        <v>14.78451845801466</v>
+        <v>14.59874666327404</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         </is>
       </c>
       <c r="E199">
-        <v>139.2257859927369</v>
+        <v>137.1547175171016</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         </is>
       </c>
       <c r="E200">
-        <v>23.12644239515632</v>
+        <v>22.73397166109087</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="E201">
-        <v>149.9473997844929</v>
+        <v>148.1893956368245</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         </is>
       </c>
       <c r="E202">
-        <v>298.1398835678542</v>
+        <v>294.4425523620734</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         </is>
       </c>
       <c r="E203">
-        <v>27.6428914790482</v>
+        <v>27.28650444600763</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         </is>
       </c>
       <c r="E204">
-        <v>12.90145029370932</v>
+        <v>12.72270710862012</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         </is>
       </c>
       <c r="E205">
-        <v>121.9869142607982</v>
+        <v>119.978904088236</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         </is>
       </c>
       <c r="E206">
-        <v>38.34667456253715</v>
+        <v>37.91850624867644</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         </is>
       </c>
       <c r="E207">
-        <v>219.0406064336874</v>
+        <v>217.2148093980351</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         </is>
       </c>
       <c r="E208">
-        <v>445.2090207907636</v>
+        <v>441.3310593833464</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -6202,7 +6202,7 @@
         </is>
       </c>
       <c r="E209">
-        <v>41.78527355266547</v>
+        <v>41.40932548038658</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         </is>
       </c>
       <c r="E210">
-        <v>21.88682376531304</v>
+        <v>21.69176707112139</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         </is>
       </c>
       <c r="E211">
-        <v>204.497573655088</v>
+        <v>202.3062533573174</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         </is>
       </c>
       <c r="E212">
-        <v>33.15178461722024</v>
+        <v>32.73385328452048</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
         </is>
       </c>
       <c r="E213">
-        <v>227.3385445960556</v>
+        <v>225.5026896355649</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         </is>
       </c>
       <c r="E214">
-        <v>449.064704364264</v>
+        <v>445.1905007227822</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
         </is>
       </c>
       <c r="E215">
-        <v>41.4234299050234</v>
+        <v>41.04914021526137</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         </is>
       </c>
       <c r="E216">
-        <v>18.84078517788049</v>
+        <v>18.65199068054901</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         </is>
       </c>
       <c r="E217">
-        <v>176.5512527532737</v>
+        <v>174.4167083950144</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         </is>
       </c>
       <c r="E218">
-        <v>30.51059148612764</v>
+        <v>30.22617062900385</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         </is>
       </c>
       <c r="E219">
-        <v>168.6013670879599</v>
+        <v>167.3741132657281</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         </is>
       </c>
       <c r="E220">
-        <v>344.9134755431817</v>
+        <v>342.3099109955025</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         </is>
       </c>
       <c r="E221">
-        <v>32.47973642113822</v>
+        <v>32.22770071287559</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         </is>
       </c>
       <c r="E222">
-        <v>17.55738557944825</v>
+        <v>17.42583043476816</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         </is>
       </c>
       <c r="E223">
-        <v>163.4088038048439</v>
+        <v>161.9459840030974</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="E224">
-        <v>26.1042993509281</v>
+        <v>25.82948089300048</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         </is>
       </c>
       <c r="E225">
-        <v>176.0747462622682</v>
+        <v>174.8389888870451</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         </is>
       </c>
       <c r="E226">
-        <v>348.8769383939675</v>
+        <v>346.2784248344167</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         </is>
       </c>
       <c r="E227">
-        <v>32.22958685933116</v>
+        <v>31.97923210343562</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         </is>
       </c>
       <c r="E228">
-        <v>14.96313960477628</v>
+        <v>14.83747335956959</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         </is>
       </c>
       <c r="E229">
-        <v>139.5972106149503</v>
+        <v>138.1875123035651</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         </is>
       </c>
       <c r="E230">
-        <v>45.73325182501218</v>
+        <v>45.4279157867618</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         </is>
       </c>
       <c r="E231">
-        <v>261.1327102650068</v>
+        <v>259.8326728674416</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         </is>
       </c>
       <c r="E232">
-        <v>532.1531058105444</v>
+        <v>529.3882266007226</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         </is>
       </c>
       <c r="E233">
-        <v>49.94540920498508</v>
+        <v>49.67733347984012</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         </is>
       </c>
       <c r="E234">
-        <v>26.68114850200096</v>
+        <v>26.54059021710159</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="E235">
-        <v>247.1431404098605</v>
+        <v>245.5739244906713</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         </is>
       </c>
       <c r="E236">
-        <v>38.57153981488098</v>
+        <v>38.27587964666406</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         </is>
       </c>
       <c r="E237">
-        <v>272.5119407540135</v>
+        <v>271.2006872379531</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="E238">
-        <v>537.1955635132811</v>
+        <v>534.4316332157144</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -7042,7 +7042,7 @@
         </is>
       </c>
       <c r="E239">
-        <v>49.42210966584343</v>
+        <v>49.15538980848626</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         </is>
       </c>
       <c r="E240">
-        <v>22.4452825326287</v>
+        <v>22.31067621281778</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         </is>
       </c>
       <c r="E241">
-        <v>208.1900293167827</v>
+        <v>206.6752158623803</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         </is>
       </c>
       <c r="E242">
-        <v>34.78728919408299</v>
+        <v>34.58664690671196</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         </is>
       </c>
       <c r="E243">
-        <v>193.6694385421548</v>
+        <v>192.8036547663776</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         </is>
       </c>
       <c r="E244">
-        <v>396.7759549268925</v>
+        <v>394.9369340353425</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         </is>
       </c>
       <c r="E245">
-        <v>37.33395043299779</v>
+        <v>37.15593608339417</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -7238,7 +7238,7 @@
         </is>
       </c>
       <c r="E246">
-        <v>20.41105293793179</v>
+        <v>20.31715203031358</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         </is>
       </c>
       <c r="E247">
-        <v>188.953846465984</v>
+        <v>187.9163987151845</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         </is>
       </c>
       <c r="E248">
-        <v>29.04855034382711</v>
+        <v>28.85651390229534</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         </is>
       </c>
       <c r="E249">
-        <v>203.3144905953797</v>
+        <v>202.4394954529913</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -7350,7 +7350,7 @@
         </is>
       </c>
       <c r="E250">
-        <v>401.6447228142716</v>
+        <v>399.8078231743337</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -7378,7 +7378,7 @@
         </is>
       </c>
       <c r="E251">
-        <v>36.98231248306251</v>
+        <v>36.80560927425002</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         </is>
       </c>
       <c r="E252">
-        <v>17.00402456844903</v>
+        <v>16.91543428646805</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="E253">
-        <v>157.5815005103976</v>
+        <v>156.5923886207626</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="E254">
-        <v>53.75394199041892</v>
+        <v>53.53348668384607</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         </is>
       </c>
       <c r="E255">
-        <v>306.5798708012879</v>
+        <v>305.6381873061196</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         </is>
       </c>
       <c r="E256">
-        <v>626.4690340352313</v>
+        <v>624.4640428080975</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -7546,7 +7546,7 @@
         </is>
       </c>
       <c r="E257">
-        <v>58.8028828744319</v>
+        <v>58.60857458298246</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         </is>
       </c>
       <c r="E258">
-        <v>31.87900792157317</v>
+        <v>31.77550423830966</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         </is>
       </c>
       <c r="E259">
-        <v>294.350375130904</v>
+        <v>293.2090069236717</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -7630,7 +7630,7 @@
         </is>
       </c>
       <c r="E260">
-        <v>44.27861977236401</v>
+        <v>44.06830377547769</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
         </is>
       </c>
       <c r="E261">
-        <v>321.610450216385</v>
+        <v>320.6553922162375</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
         </is>
       </c>
       <c r="E262">
-        <v>632.8744856648864</v>
+        <v>630.8679917737958</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="E263">
-        <v>58.08602944799635</v>
+        <v>57.89293865228385</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -7742,7 +7742,7 @@
         </is>
       </c>
       <c r="E264">
-        <v>26.23063057874112</v>
+        <v>26.13338084000229</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         </is>
       </c>
       <c r="E265">
-        <v>242.2520795436459</v>
+        <v>241.1683523311125</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         </is>
       </c>
       <c r="E266">
-        <v>39.16607371642386</v>
+        <v>39.01655472785239</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -7826,7 +7826,7 @@
         </is>
       </c>
       <c r="E267">
-        <v>219.4641220948355</v>
+        <v>218.8158994084961</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         </is>
       </c>
       <c r="E268">
-        <v>450.3110974119057</v>
+        <v>448.9326938719061</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         </is>
       </c>
       <c r="E269">
-        <v>42.34276774611015</v>
+        <v>42.20942557555635</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         </is>
       </c>
       <c r="E270">
-        <v>23.31782215918267</v>
+        <v>23.24637037637842</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
         </is>
       </c>
       <c r="E271">
-        <v>215.6820102524257</v>
+        <v>214.9022339793894</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
         </is>
       </c>
       <c r="E272">
-        <v>31.94274388286608</v>
+        <v>31.80201951469289</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         </is>
       </c>
       <c r="E273">
-        <v>231.5451816989694</v>
+        <v>230.8859863215621</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         </is>
       </c>
       <c r="E274">
-        <v>456.1595061999438</v>
+        <v>454.7808838628251</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         </is>
       </c>
       <c r="E275">
-        <v>41.87499058731556</v>
+        <v>41.74279420161389</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         </is>
       </c>
       <c r="E276">
-        <v>18.99766416608917</v>
+        <v>18.93165660073548</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -8106,7 +8106,7 @@
         </is>
       </c>
       <c r="E277">
-        <v>175.7414205373397</v>
+        <v>175.0116880640841</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         </is>
       </c>
       <c r="E278">
-        <v>62.39539360967075</v>
+        <v>62.22473443583666</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="E279">
-        <v>355.2856834831792</v>
+        <v>354.5499143518996</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         </is>
       </c>
       <c r="E280">
-        <v>727.9594313889988</v>
+        <v>726.391217845532</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         </is>
       </c>
       <c r="E281">
-        <v>68.33962686892215</v>
+        <v>68.18783331863206</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         </is>
       </c>
       <c r="E282">
-        <v>37.45586519603071</v>
+        <v>37.37313184469673</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
         </is>
       </c>
       <c r="E283">
-        <v>346.036856391433</v>
+        <v>345.1424729304265</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="E284">
-        <v>50.23313271248252</v>
+        <v>50.07439136606543</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         </is>
       </c>
       <c r="E285">
-        <v>374.5955168214569</v>
+        <v>373.8426638909946</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         </is>
       </c>
       <c r="E286">
-        <v>735.924941308402</v>
+        <v>734.3529006051515</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         </is>
       </c>
       <c r="E287">
-        <v>67.39506081698762</v>
+        <v>67.24453102666051</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         </is>
       </c>
       <c r="E288">
-        <v>30.15562982505392</v>
+        <v>30.0802655121316</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
         </is>
       </c>
       <c r="E289">
-        <v>278.4474239912751</v>
+        <v>277.6214237270643</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -8470,7 +8470,7 @@
         </is>
       </c>
       <c r="E290">
-        <v>43.45879947203622</v>
+        <v>43.33806988354823</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         </is>
       </c>
       <c r="E291">
-        <v>245.0997916950657</v>
+        <v>244.5704586109508</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         </is>
       </c>
       <c r="E292">
-        <v>503.6080984735628</v>
+        <v>502.4814407077376</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
         </is>
       </c>
       <c r="E293">
-        <v>47.32315257946806</v>
+        <v>47.21432062251997</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         </is>
       </c>
       <c r="E294">
-        <v>26.17402981396536</v>
+        <v>26.11438271752548</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         </is>
       </c>
       <c r="E295">
-        <v>242.4672830048968</v>
+        <v>241.829067784195</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         </is>
       </c>
       <c r="E296">
-        <v>34.63981594532976</v>
+        <v>34.52929824108642</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         </is>
       </c>
       <c r="E297">
-        <v>259.8260034967838</v>
+        <v>259.2825289468092</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         </is>
       </c>
       <c r="E298">
-        <v>510.4924601071553</v>
+        <v>509.363422964249</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -8722,7 +8722,7 @@
         </is>
       </c>
       <c r="E299">
-        <v>46.72842160909076</v>
+        <v>46.62074746037678</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
         </is>
       </c>
       <c r="E300">
-        <v>20.86270688562471</v>
+        <v>20.80939759493885</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         </is>
       </c>
       <c r="E301">
-        <v>193.1593655960522</v>
+        <v>192.5798874763714</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -8806,7 +8806,7 @@
         </is>
       </c>
       <c r="E302">
-        <v>71.35882765174156</v>
+        <v>71.21289177240142</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         </is>
       </c>
       <c r="E303">
-        <v>405.9203053674846</v>
+        <v>405.2807014165218</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -8862,7 +8862,7 @@
         </is>
       </c>
       <c r="E304">
-        <v>833.762942000944</v>
+        <v>832.3983043788053</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         </is>
       </c>
       <c r="E305">
-        <v>78.27979128177519</v>
+        <v>78.14797917593191</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         </is>
       </c>
       <c r="E306">
-        <v>43.25165604007444</v>
+        <v>43.17762875250049</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -8946,7 +8946,7 @@
         </is>
       </c>
       <c r="E307">
-        <v>400.5250957348698</v>
+        <v>399.7462373173929</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         </is>
       </c>
       <c r="E308">
-        <v>56.18255182000233</v>
+        <v>56.05197232221478</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         </is>
       </c>
       <c r="E309">
-        <v>430.0832843166181</v>
+        <v>429.4205754961751</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         </is>
       </c>
       <c r="E310">
-        <v>843.4662696155034</v>
+        <v>842.0951348931141</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         </is>
       </c>
       <c r="E311">
-        <v>77.07761200201944</v>
+        <v>76.94730226355111</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         </is>
       </c>
       <c r="E312">
-        <v>34.08245835657188</v>
+        <v>34.01795793623789</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         </is>
       </c>
       <c r="E313">
-        <v>315.3014321652144</v>
+        <v>314.6114057541525</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         </is>
       </c>
       <c r="E314">
-        <v>47.56756882037279</v>
+        <v>47.46157814587641</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="E315">
-        <v>270.1541809882002</v>
+        <v>269.6808383798389</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         </is>
       </c>
       <c r="E316">
-        <v>555.7416454315671</v>
+        <v>554.733293362386</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         </is>
       </c>
       <c r="E317">
-        <v>52.18551227602266</v>
+        <v>52.08833184760498</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         </is>
       </c>
       <c r="E318">
-        <v>28.94335386017134</v>
+        <v>28.88852475028901</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -9282,7 +9282,7 @@
         </is>
       </c>
       <c r="E319">
-        <v>268.724093517003</v>
+        <v>268.1528571865934</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         </is>
       </c>
       <c r="E320">
-        <v>37.0735582959031</v>
+        <v>36.98045549421235</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         </is>
       </c>
       <c r="E321">
-        <v>287.6930689415428</v>
+        <v>287.2007047549921</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -9366,7 +9366,7 @@
         </is>
       </c>
       <c r="E322">
-        <v>563.7046523395406</v>
+        <v>562.6915763881241</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -9394,7 +9394,7 @@
         </is>
       </c>
       <c r="E323">
-        <v>51.4559985739633</v>
+        <v>51.3601403320269</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -9422,7 +9422,7 @@
         </is>
       </c>
       <c r="E324">
-        <v>22.57684639913724</v>
+        <v>22.5300443508099</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -9450,7 +9450,7 @@
         </is>
       </c>
       <c r="E325">
-        <v>209.4088256307994</v>
+        <v>208.9123970518994</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         </is>
       </c>
       <c r="E326">
-        <v>80.44216291810862</v>
+        <v>80.30394491314622</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         </is>
       </c>
       <c r="E327">
-        <v>457.6880643978816</v>
+        <v>457.068591254104</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         </is>
       </c>
       <c r="E328">
-        <v>942.140644741237</v>
+        <v>940.8176258221274</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         </is>
       </c>
       <c r="E329">
-        <v>88.45313033029929</v>
+        <v>88.32569282222551</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -9590,7 +9590,7 @@
         </is>
       </c>
       <c r="E330">
-        <v>49.18564465033947</v>
+        <v>49.11162898900771</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
         </is>
       </c>
       <c r="E331">
-        <v>456.7196974225647</v>
+        <v>455.9646150717354</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -9646,7 +9646,7 @@
         </is>
       </c>
       <c r="E332">
-        <v>61.96944906126543</v>
+        <v>61.85200031243119</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         </is>
       </c>
       <c r="E333">
-        <v>487.2274924270953</v>
+        <v>486.5758970424122</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         </is>
       </c>
       <c r="E334">
-        <v>953.7417179833716</v>
+        <v>952.4087896084325</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         </is>
       </c>
       <c r="E335">
-        <v>86.96762352809148</v>
+        <v>86.84212933399699</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -9758,7 +9758,7 @@
         </is>
       </c>
       <c r="E336">
-        <v>37.94671516863208</v>
+        <v>37.88564173356434</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
         </is>
       </c>
       <c r="E337">
-        <v>351.9126143639949</v>
+        <v>351.2785725872276</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
         </is>
       </c>
       <c r="E338">
-        <v>51.30066473436501</v>
+        <v>51.19914976443967</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         </is>
       </c>
       <c r="E339">
-        <v>293.8911860517866</v>
+        <v>293.426647259048</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -9870,7 +9870,7 @@
         </is>
       </c>
       <c r="E340">
-        <v>605.0714077199985</v>
+        <v>604.0811182063713</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         </is>
       </c>
       <c r="E341">
-        <v>56.76891191190968</v>
+        <v>56.67375476673552</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         </is>
       </c>
       <c r="E342">
-        <v>31.53282273341219</v>
+        <v>31.477399024379</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         </is>
       </c>
       <c r="E343">
-        <v>293.36296342587</v>
+        <v>292.8026348442866</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         </is>
       </c>
       <c r="E344">
-        <v>39.13344318777985</v>
+        <v>39.04886918731869</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         </is>
       </c>
       <c r="E345">
-        <v>314.291011085334</v>
+        <v>313.800520908138</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -10038,7 +10038,7 @@
         </is>
       </c>
       <c r="E346">
-        <v>614.1131500234136</v>
+        <v>613.1153697087879</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
         </is>
       </c>
       <c r="E347">
-        <v>55.90392800554211</v>
+        <v>55.81040671507491</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         </is>
       </c>
       <c r="E348">
-        <v>24.09032414150979</v>
+        <v>24.04550495904859</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -10122,7 +10122,7 @@
         </is>
       </c>
       <c r="E349">
-        <v>223.8395738445238</v>
+        <v>223.3783915216407</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -10150,7 +10150,7 @@
         </is>
       </c>
       <c r="E350">
-        <v>89.01249521383649</v>
+        <v>88.86862636109419</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -10178,7 +10178,7 @@
         </is>
       </c>
       <c r="E351">
-        <v>508.0304503862376</v>
+        <v>507.3692057020679</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         </is>
       </c>
       <c r="E352">
-        <v>1047.479447010292</v>
+        <v>1046.066067822949</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         </is>
       </c>
       <c r="E353">
-        <v>98.31247722728232</v>
+        <v>98.17674985416427</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -10262,7 +10262,7 @@
         </is>
       </c>
       <c r="E354">
-        <v>54.91632127715145</v>
+        <v>54.83499303149127</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -10290,7 +10290,7 @@
         </is>
       </c>
       <c r="E355">
-        <v>511.093367368205</v>
+        <v>510.2874228739666</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         </is>
       </c>
       <c r="E356">
-        <v>67.16982228702729</v>
+        <v>67.05440623824661</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -10346,7 +10346,7 @@
         </is>
       </c>
       <c r="E357">
-        <v>543.1644498795323</v>
+        <v>542.4584611647197</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         </is>
       </c>
       <c r="E358">
-        <v>1061.031516384787</v>
+        <v>1059.603793035069</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -10402,7 +10402,7 @@
         </is>
       </c>
       <c r="E359">
-        <v>96.53652681736585</v>
+        <v>96.40340358034686</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         </is>
       </c>
       <c r="E360">
-        <v>41.5213553673038</v>
+        <v>41.45785699389418</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -10458,7 +10458,7 @@
         </is>
       </c>
       <c r="E361">
-        <v>385.8822736218518</v>
+        <v>385.2433488123221</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
         </is>
       </c>
       <c r="E362">
-        <v>54.58586584645105</v>
+        <v>54.47895336667033</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -10514,7 +10514,7 @@
         </is>
       </c>
       <c r="E363">
-        <v>316.170539335572</v>
+        <v>315.667718275252</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         </is>
       </c>
       <c r="E364">
-        <v>651.2206568217365</v>
+        <v>650.1482512199689</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
         </is>
       </c>
       <c r="E365">
-        <v>61.03271504478931</v>
+        <v>60.93000023335622</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -10598,7 +10598,7 @@
         </is>
       </c>
       <c r="E366">
-        <v>33.91526330366499</v>
+        <v>33.85369544875297</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         </is>
       </c>
       <c r="E367">
-        <v>315.9933796586562</v>
+        <v>315.3878825160953</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         </is>
       </c>
       <c r="E368">
-        <v>40.80461276789335</v>
+        <v>40.72056847220276</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         </is>
       </c>
       <c r="E369">
-        <v>339.3956848429938</v>
+        <v>338.857000020605</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         </is>
       </c>
       <c r="E370">
-        <v>661.3100864292312</v>
+        <v>660.226596438832</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         </is>
       </c>
       <c r="E371">
-        <v>60.03651840631039</v>
+        <v>59.93593632152439</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -10766,7 +10766,7 @@
         </is>
       </c>
       <c r="E372">
-        <v>25.40578965047564</v>
+        <v>25.35862907618245</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -10794,7 +10794,7 @@
         </is>
       </c>
       <c r="E373">
-        <v>236.3674533435957</v>
+        <v>235.8968795735886</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         </is>
       </c>
       <c r="E374">
-        <v>96.79124644221058</v>
+        <v>96.62734374646473</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         </is>
       </c>
       <c r="E375">
-        <v>556.0636759709638</v>
+        <v>555.2913000537808</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="E376">
-        <v>1147.735598591422</v>
+        <v>1146.083873242531</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         </is>
       </c>
       <c r="E377">
-        <v>107.6523831352575</v>
+        <v>107.4942317954058</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         </is>
       </c>
       <c r="E378">
-        <v>60.30492420065087</v>
+        <v>60.20785292199501</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
         </is>
       </c>
       <c r="E379">
-        <v>562.1306079659944</v>
+        <v>561.1903133506472</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -10990,7 +10990,7 @@
         </is>
       </c>
       <c r="E380">
-        <v>71.64121258339651</v>
+        <v>71.51673078172402</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -11018,7 +11018,7 @@
         </is>
       </c>
       <c r="E381">
-        <v>596.8156157456976</v>
+        <v>595.9805014883492</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         </is>
       </c>
       <c r="E382">
-        <v>1163.224876665382</v>
+        <v>1161.552706830788</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -11074,7 +11074,7 @@
         </is>
       </c>
       <c r="E383">
-        <v>105.5911557610409</v>
+        <v>105.4365728926654</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         </is>
       </c>
       <c r="E384">
-        <v>44.74012934026507</v>
+        <v>44.66792600322604</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -11130,7 +11130,7 @@
         </is>
       </c>
       <c r="E385">
-        <v>416.4198370505941</v>
+        <v>415.7126625700808</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
